--- a/RiskHalo_Certification_Challenge/data/Weekly_Trade_Data_Uploads/Week_11_Trade_data.xlsx
+++ b/RiskHalo_Certification_Challenge/data/Weekly_Trade_Data_Uploads/Week_11_Trade_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SOFTWARES\CodeRepo\AIE9_CERTIFICATION_CHALLENGE\RiskHalo_Certification_Challenge\data\Weekly_Trade_Data_Uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F96C974B-4E84-49D2-B74B-13F45453BEB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A37E3BBC-7B19-448D-9076-2D0047380D6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="37">
   <si>
     <t>Sr.</t>
   </si>
@@ -55,46 +55,70 @@
     <t>Turnover</t>
   </si>
   <si>
-    <t>OPT NIFTY 03 Jul 2025 25000 PE</t>
-  </si>
-  <si>
-    <t>23-06-2025</t>
-  </si>
-  <si>
-    <t>OPT NIFTY 26 Jun 2025 25200 CE</t>
-  </si>
-  <si>
-    <t>24-06-2025</t>
-  </si>
-  <si>
-    <t>25-06-2025</t>
-  </si>
-  <si>
-    <t>OPT NIFTY 26 Jun 2025 25200 PE</t>
-  </si>
-  <si>
-    <t>OPT ACC 31 Jul 2025 1860 CE</t>
-  </si>
-  <si>
-    <t>26-06-2025</t>
-  </si>
-  <si>
-    <t>OPT BAJFINANCE 31 Jul 2025 950 CE</t>
-  </si>
-  <si>
-    <t>OPT NIFTY 26 Jun 2025 25300 CE</t>
-  </si>
-  <si>
-    <t>OPT BPCL 31 Jul 2025 320 CE</t>
-  </si>
-  <si>
-    <t>OPT NIFTY 03 Jul 2025 25600 PE</t>
-  </si>
-  <si>
-    <t>27-06-2025</t>
-  </si>
-  <si>
-    <t>OPT NIFTY 03 Jul 2025 25500 CE</t>
+    <t>OPT DLF 31 Jul 2025 800 PE</t>
+  </si>
+  <si>
+    <t>28-07-2025</t>
+  </si>
+  <si>
+    <t>OPT LODHA 31 Jul 2025 1220 PE</t>
+  </si>
+  <si>
+    <t>OPT LAURUSLABS 31 Jul 2025 880 CE</t>
+  </si>
+  <si>
+    <t>OPT LAURUSLABS 31 Jul 2025 890 PE</t>
+  </si>
+  <si>
+    <t>OPT PETRONET 31 Jul 2025 300 PE</t>
+  </si>
+  <si>
+    <t>29-07-2025</t>
+  </si>
+  <si>
+    <t>OPT TORNTPHARM 31 Jul 2025 3700 CE</t>
+  </si>
+  <si>
+    <t>OPT JSWSTEEL 31 Jul 2025 1050 CE</t>
+  </si>
+  <si>
+    <t>OPT VBL 31 Jul 2025 530 CE</t>
+  </si>
+  <si>
+    <t>30-07-2025</t>
+  </si>
+  <si>
+    <t>OPT POONAWALLA 31 Jul 2025 430 CE</t>
+  </si>
+  <si>
+    <t>OPT BOSCHLTD 31 Jul 2025 39500 PE</t>
+  </si>
+  <si>
+    <t>OPT HINDUNILVR 28 Aug 2025 2500 CE</t>
+  </si>
+  <si>
+    <t>31-07-2025</t>
+  </si>
+  <si>
+    <t>OPT ZYDUSLIFE 28 Aug 2025 980 PE</t>
+  </si>
+  <si>
+    <t>OPT KAYNES 28 Aug 2025 6100 PE</t>
+  </si>
+  <si>
+    <t>OPT KAYNES 28 Aug 2025 6000 CE</t>
+  </si>
+  <si>
+    <t>OPT HINDUNILVR 28 Aug 2025 2560 PE</t>
+  </si>
+  <si>
+    <t>01-08-2025</t>
+  </si>
+  <si>
+    <t>OPT HINDUNILVR 28 Aug 2025 2560 CE</t>
+  </si>
+  <si>
+    <t>OPT DIVISLAB 28 Aug 2025 6400 PE</t>
   </si>
   <si>
     <t>Buy Qty</t>
@@ -447,10 +471,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="35.7109375" customWidth="1"/>
+    <col min="2" max="2" width="32.140625" customWidth="1"/>
     <col min="3" max="3" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.140625" style="1"/>
   </cols>
@@ -466,10 +490,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -478,10 +502,10 @@
         <v>4</v>
       </c>
       <c r="H1" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="I1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="J1" t="s">
         <v>5</v>
@@ -504,472 +528,801 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>205</v>
+        <v>91</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="1">
-        <v>45831</v>
+        <v>45866</v>
       </c>
       <c r="D2">
-        <v>75</v>
+        <v>1650</v>
       </c>
       <c r="E2">
-        <v>284.25</v>
+        <v>10.15</v>
       </c>
       <c r="F2">
-        <v>21318.75</v>
+        <v>16747.5</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H2">
-        <v>75</v>
+        <v>1650</v>
       </c>
       <c r="I2">
-        <v>316.05</v>
+        <v>11.55</v>
       </c>
       <c r="J2">
-        <v>23703.75</v>
+        <v>19057.5</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>2385</v>
+        <v>2310</v>
       </c>
       <c r="M2">
-        <v>91.14</v>
+        <v>105.41</v>
       </c>
       <c r="N2">
-        <v>2293.86</v>
+        <v>2204.59</v>
       </c>
       <c r="O2">
-        <v>2385</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>207</v>
+        <v>166</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="1">
-        <v>45832</v>
+        <v>45866</v>
       </c>
       <c r="D3">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="E3">
-        <v>168.03</v>
+        <v>19.7</v>
       </c>
       <c r="F3">
-        <v>50407.5</v>
+        <v>8865</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H3">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="I3">
-        <v>166.09</v>
+        <v>12.5</v>
       </c>
       <c r="J3">
-        <v>49826.25</v>
+        <v>5625</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>-581.25</v>
+        <v>-3240</v>
       </c>
       <c r="M3">
-        <v>282.94</v>
+        <v>59.19</v>
       </c>
       <c r="N3">
-        <v>-864.19</v>
+        <v>-3299.19</v>
       </c>
       <c r="O3">
-        <v>581.25</v>
+        <v>3240</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>208</v>
+        <v>161</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1">
-        <v>45833</v>
+        <v>45866</v>
       </c>
       <c r="D4">
-        <v>150</v>
+        <v>1700</v>
       </c>
       <c r="E4">
-        <v>85.33</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="F4">
-        <v>12798.75</v>
+        <v>32470</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H4">
-        <v>150</v>
+        <v>1700</v>
       </c>
       <c r="I4">
-        <v>88.08</v>
+        <v>23.1</v>
       </c>
       <c r="J4">
-        <v>13211.25</v>
+        <v>39270</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>412.5</v>
+        <v>6800</v>
       </c>
       <c r="M4">
-        <v>118.62</v>
+        <v>117.98</v>
       </c>
       <c r="N4">
-        <v>293.88</v>
+        <v>6682.02</v>
       </c>
       <c r="O4">
-        <v>412.5</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>210</v>
+        <v>163</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1">
-        <v>45833</v>
+        <v>45866</v>
       </c>
       <c r="D5">
-        <v>300</v>
+        <v>1700</v>
       </c>
       <c r="E5">
-        <v>73.69</v>
+        <v>15.75</v>
       </c>
       <c r="F5">
-        <v>22106.25</v>
+        <v>26775</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H5">
-        <v>300</v>
+        <v>1700</v>
       </c>
       <c r="I5">
-        <v>70.209999999999994</v>
+        <v>13.6</v>
       </c>
       <c r="J5">
-        <v>21063.75</v>
+        <v>23120</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>-1042.5</v>
+        <v>-3655</v>
       </c>
       <c r="M5">
-        <v>228.67</v>
+        <v>92.1</v>
       </c>
       <c r="N5">
-        <v>-1271.17</v>
+        <v>-3747.1</v>
       </c>
       <c r="O5">
-        <v>1042.5</v>
+        <v>3655</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>1</v>
+        <v>229</v>
       </c>
       <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1">
+        <v>45867</v>
+      </c>
+      <c r="D6">
+        <v>5400</v>
+      </c>
+      <c r="E6">
+        <v>7.17</v>
+      </c>
+      <c r="F6">
+        <v>38700</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="1">
-        <v>45834</v>
-      </c>
-      <c r="D6">
-        <v>600</v>
-      </c>
-      <c r="E6">
-        <v>69.08</v>
-      </c>
-      <c r="F6">
-        <v>41445</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="H6">
-        <v>600</v>
+        <v>5400</v>
       </c>
       <c r="I6">
-        <v>68.5</v>
+        <v>6.77</v>
       </c>
       <c r="J6">
-        <v>41100</v>
+        <v>36540</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>-345</v>
+        <v>-2160</v>
       </c>
       <c r="M6">
-        <v>171.45</v>
+        <v>210.93</v>
       </c>
       <c r="N6">
-        <v>-516.45000000000005</v>
+        <v>-2370.9299999999998</v>
       </c>
       <c r="O6">
-        <v>345</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>35</v>
+        <v>281</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" s="1">
-        <v>45834</v>
+        <v>45867</v>
       </c>
       <c r="D7">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="E7">
-        <v>32.799999999999997</v>
+        <v>79.2</v>
       </c>
       <c r="F7">
-        <v>24600</v>
+        <v>19800</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H7">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="I7">
-        <v>31.3</v>
+        <v>76</v>
       </c>
       <c r="J7">
-        <v>23475</v>
+        <v>19000</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>-1125</v>
+        <v>-800</v>
       </c>
       <c r="M7">
-        <v>91.63</v>
+        <v>82.97</v>
       </c>
       <c r="N7">
-        <v>-1216.6300000000001</v>
+        <v>-882.97</v>
       </c>
       <c r="O7">
-        <v>1125</v>
+        <v>800</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>211</v>
+        <v>146</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" s="1">
-        <v>45834</v>
+        <v>45867</v>
       </c>
       <c r="D8">
-        <v>75</v>
+        <v>675</v>
       </c>
       <c r="E8">
-        <v>109.3</v>
+        <v>11.1</v>
       </c>
       <c r="F8">
-        <v>8197.5</v>
+        <v>7492.5</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H8">
-        <v>75</v>
+        <v>675</v>
       </c>
       <c r="I8">
-        <v>114.6</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="J8">
-        <v>8595</v>
+        <v>6615</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>397.5</v>
+        <v>-877.5</v>
       </c>
       <c r="M8">
-        <v>63.11</v>
+        <v>59.97</v>
       </c>
       <c r="N8">
-        <v>334.39</v>
+        <v>-937.47</v>
       </c>
       <c r="O8">
-        <v>397.5</v>
+        <v>877.5</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>52</v>
+        <v>286</v>
       </c>
       <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="1">
+        <v>45868</v>
+      </c>
+      <c r="D9">
+        <v>1025</v>
+      </c>
+      <c r="E9">
+        <v>3.35</v>
+      </c>
+      <c r="F9">
+        <v>3433.75</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="1">
-        <v>45834</v>
-      </c>
-      <c r="D9">
-        <v>1975</v>
-      </c>
-      <c r="E9">
-        <v>13.2</v>
-      </c>
-      <c r="F9">
-        <v>26070</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="H9">
-        <v>1975</v>
+        <v>1025</v>
       </c>
       <c r="I9">
-        <v>13.6</v>
+        <v>1.95</v>
       </c>
       <c r="J9">
-        <v>26860</v>
+        <v>1998.75</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>790</v>
+        <v>-1435</v>
       </c>
       <c r="M9">
-        <v>97.04</v>
+        <v>51.58</v>
       </c>
       <c r="N9">
-        <v>692.96</v>
+        <v>-1486.58</v>
       </c>
       <c r="O9">
-        <v>790</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>215</v>
+        <v>241</v>
       </c>
       <c r="B10" t="s">
         <v>22</v>
       </c>
       <c r="C10" s="1">
-        <v>45835</v>
+        <v>45868</v>
       </c>
       <c r="D10">
-        <v>75</v>
+        <v>1700</v>
       </c>
       <c r="E10">
-        <v>146.69999999999999</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="F10">
-        <v>11002.5</v>
+        <v>3910</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H10">
-        <v>75</v>
+        <v>1700</v>
       </c>
       <c r="I10">
-        <v>148.30000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="J10">
-        <v>11122.5</v>
+        <v>2550</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>120</v>
+        <v>-1360</v>
       </c>
       <c r="M10">
-        <v>67.95</v>
+        <v>52.59</v>
       </c>
       <c r="N10">
-        <v>52.05</v>
+        <v>-1412.59</v>
       </c>
       <c r="O10">
-        <v>120</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>213</v>
+        <v>49</v>
       </c>
       <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1">
+        <v>45868</v>
+      </c>
+      <c r="D11">
+        <v>75</v>
+      </c>
+      <c r="E11">
+        <v>159.33000000000001</v>
+      </c>
+      <c r="F11">
+        <v>11950</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11">
+        <v>75</v>
+      </c>
+      <c r="I11">
+        <v>145</v>
+      </c>
+      <c r="J11">
+        <v>10875</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>-1075</v>
+      </c>
+      <c r="M11">
+        <v>91.61</v>
+      </c>
+      <c r="N11">
+        <v>-1166.6099999999999</v>
+      </c>
+      <c r="O11">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>117</v>
+      </c>
+      <c r="B12" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="1">
-        <v>45835</v>
-      </c>
-      <c r="D11">
-        <v>225</v>
-      </c>
-      <c r="E11">
-        <v>214.55</v>
-      </c>
-      <c r="F11">
-        <v>48273.75</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11">
-        <v>225</v>
-      </c>
-      <c r="I11">
-        <v>221.32</v>
-      </c>
-      <c r="J11">
-        <v>49796.25</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>1522.5</v>
-      </c>
-      <c r="M11">
-        <v>210.78</v>
-      </c>
-      <c r="N11">
-        <v>1311.72</v>
-      </c>
-      <c r="O11">
-        <v>1522.5</v>
+      <c r="C12" s="1">
+        <v>45869</v>
+      </c>
+      <c r="D12">
+        <v>300</v>
+      </c>
+      <c r="E12">
+        <v>75.099999999999994</v>
+      </c>
+      <c r="F12">
+        <v>22530</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12">
+        <v>300</v>
+      </c>
+      <c r="I12">
+        <v>85</v>
+      </c>
+      <c r="J12">
+        <v>25500</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>2970</v>
+      </c>
+      <c r="M12">
+        <v>93.57</v>
+      </c>
+      <c r="N12">
+        <v>2876.43</v>
+      </c>
+      <c r="O12">
+        <v>2970</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>290</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="1">
+        <v>45869</v>
+      </c>
+      <c r="D13">
+        <v>1800</v>
+      </c>
+      <c r="E13">
+        <v>35.479999999999997</v>
+      </c>
+      <c r="F13">
+        <v>63855</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13">
+        <v>1800</v>
+      </c>
+      <c r="I13">
+        <v>31.63</v>
+      </c>
+      <c r="J13">
+        <v>56925</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>-6930</v>
+      </c>
+      <c r="M13">
+        <v>180.43</v>
+      </c>
+      <c r="N13">
+        <v>-7110.43</v>
+      </c>
+      <c r="O13">
+        <v>6930</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>153</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="1">
+        <v>45869</v>
+      </c>
+      <c r="D14">
+        <v>1000</v>
+      </c>
+      <c r="E14">
+        <v>206.8</v>
+      </c>
+      <c r="F14">
+        <v>206800</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14">
+        <v>1000</v>
+      </c>
+      <c r="I14">
+        <v>210.6</v>
+      </c>
+      <c r="J14">
+        <v>210599.98</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>3799.98</v>
+      </c>
+      <c r="M14">
+        <v>534.12</v>
+      </c>
+      <c r="N14">
+        <v>3265.86</v>
+      </c>
+      <c r="O14">
+        <v>3799.98</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>151</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="1">
+        <v>45869</v>
+      </c>
+      <c r="D15">
+        <v>200</v>
+      </c>
+      <c r="E15">
+        <v>323.55</v>
+      </c>
+      <c r="F15">
+        <v>64710</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15">
+        <v>200</v>
+      </c>
+      <c r="I15">
+        <v>330</v>
+      </c>
+      <c r="J15">
+        <v>66000</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>1290</v>
+      </c>
+      <c r="M15">
+        <v>170.1</v>
+      </c>
+      <c r="N15">
+        <v>1119.9000000000001</v>
+      </c>
+      <c r="O15">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>120</v>
+      </c>
+      <c r="B16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="1">
+        <v>45870</v>
+      </c>
+      <c r="D16">
+        <v>300</v>
+      </c>
+      <c r="E16">
+        <v>48</v>
+      </c>
+      <c r="F16">
+        <v>14400</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16">
+        <v>300</v>
+      </c>
+      <c r="I16">
+        <v>45.15</v>
+      </c>
+      <c r="J16">
+        <v>13545</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>-855</v>
+      </c>
+      <c r="M16">
+        <v>72.930000000000007</v>
+      </c>
+      <c r="N16">
+        <v>-927.93</v>
+      </c>
+      <c r="O16">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>118</v>
+      </c>
+      <c r="B17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="1">
+        <v>45870</v>
+      </c>
+      <c r="D17">
+        <v>300</v>
+      </c>
+      <c r="E17">
+        <v>63.65</v>
+      </c>
+      <c r="F17">
+        <v>19095</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H17">
+        <v>300</v>
+      </c>
+      <c r="I17">
+        <v>60.55</v>
+      </c>
+      <c r="J17">
+        <v>18165</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>-930</v>
+      </c>
+      <c r="M17">
+        <v>82.29</v>
+      </c>
+      <c r="N17">
+        <v>-1012.29</v>
+      </c>
+      <c r="O17">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>86</v>
+      </c>
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="1">
+        <v>45870</v>
+      </c>
+      <c r="D18">
+        <v>100</v>
+      </c>
+      <c r="E18">
+        <v>174.85</v>
+      </c>
+      <c r="F18">
+        <v>17485</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H18">
+        <v>100</v>
+      </c>
+      <c r="I18">
+        <v>170.75</v>
+      </c>
+      <c r="J18">
+        <v>17075</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>-410</v>
+      </c>
+      <c r="M18">
+        <v>79.33</v>
+      </c>
+      <c r="N18">
+        <v>-489.33</v>
+      </c>
+      <c r="O18">
+        <v>410</v>
       </c>
     </row>
   </sheetData>
